--- a/man/tables/ae_detail_EXAMPLE_STUDY__30OCT2020.xlsx
+++ b/man/tables/ae_detail_EXAMPLE_STUDY__30OCT2020.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="161">
   <si>
     <t xml:space="preserve">Category</t>
   </si>
@@ -72,9 +72,6 @@
   </si>
   <si>
     <t xml:space="preserve">ATRIAL FIBRILLATION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33</t>
   </si>
   <si>
     <t xml:space="preserve">ATRIAL FLUTTER</t>
@@ -1025,22 +1022,22 @@
   <sheetData>
     <row r="1" ht="50" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" ht="82" customHeight="1">
@@ -1174,7 +1171,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -1188,13 +1185,13 @@
         <v>18</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>0</v>
@@ -1208,13 +1205,13 @@
         <v>18</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -1228,13 +1225,13 @@
         <v>18</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E18" s="3" t="n">
         <v>0</v>
@@ -1248,13 +1245,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1268,13 +1265,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>0</v>
@@ -1285,16 +1282,16 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="C21" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
@@ -1305,16 +1302,16 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="C22" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>0</v>
@@ -1325,16 +1322,16 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="C23" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>0</v>
@@ -1345,16 +1342,16 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C24" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>0</v>
@@ -1365,16 +1362,16 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>0</v>
@@ -1385,16 +1382,16 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>0</v>
@@ -1405,10 +1402,10 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>1</v>
@@ -1425,10 +1422,10 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>2</v>
@@ -1445,10 +1442,10 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>4</v>
@@ -1465,10 +1462,10 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>5</v>
@@ -1480,21 +1477,21 @@
         <v>1</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>0</v>
@@ -1505,10 +1502,10 @@
     </row>
     <row r="32">
       <c r="A32" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C32" s="3" t="n">
         <v>1</v>
@@ -1525,10 +1522,10 @@
     </row>
     <row r="33">
       <c r="A33" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C33" s="3" t="n">
         <v>1</v>
@@ -1545,10 +1542,10 @@
     </row>
     <row r="34">
       <c r="A34" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>1</v>
@@ -1565,10 +1562,10 @@
     </row>
     <row r="35">
       <c r="A35" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C35" s="3" t="n">
         <v>1</v>
@@ -1585,10 +1582,10 @@
     </row>
     <row r="36">
       <c r="A36" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>5</v>
@@ -1605,10 +1602,10 @@
     </row>
     <row r="37">
       <c r="A37" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C37" s="3" t="n">
         <v>1</v>
@@ -1625,10 +1622,10 @@
     </row>
     <row r="38">
       <c r="A38" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C38" s="3" t="n">
         <v>1</v>
@@ -1645,10 +1642,10 @@
     </row>
     <row r="39">
       <c r="A39" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39" s="3" t="n">
         <v>1</v>
@@ -1660,15 +1657,15 @@
         <v>1</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>5</v>
@@ -1685,10 +1682,10 @@
     </row>
     <row r="41">
       <c r="A41" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="C41" s="3" t="n">
         <v>2</v>
@@ -1705,10 +1702,10 @@
     </row>
     <row r="42">
       <c r="A42" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C42" s="3" t="n">
         <v>5</v>
@@ -1725,10 +1722,10 @@
     </row>
     <row r="43">
       <c r="A43" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C43" s="3" t="n">
         <v>5</v>
@@ -1740,15 +1737,15 @@
         <v>1</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C44" s="3" t="n">
         <v>2</v>
@@ -1765,10 +1762,10 @@
     </row>
     <row r="45">
       <c r="A45" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C45" s="3" t="n">
         <v>1</v>
@@ -1785,10 +1782,10 @@
     </row>
     <row r="46">
       <c r="A46" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C46" s="3" t="n">
         <v>1</v>
@@ -1805,10 +1802,10 @@
     </row>
     <row r="47">
       <c r="A47" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C47" s="3" t="n">
         <v>2</v>
@@ -1825,10 +1822,10 @@
     </row>
     <row r="48">
       <c r="A48" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>1</v>
@@ -1845,70 +1842,70 @@
     </row>
     <row r="49">
       <c r="A49" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="C49" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E49" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C50" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E50" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="C51" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E51" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="C52" s="3" t="n">
         <v>1</v>
@@ -1925,10 +1922,10 @@
     </row>
     <row r="53">
       <c r="A53" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C53" s="3" t="n">
         <v>1</v>
@@ -1945,10 +1942,10 @@
     </row>
     <row r="54">
       <c r="A54" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C54" s="3" t="n">
         <v>1</v>
@@ -1965,10 +1962,10 @@
     </row>
     <row r="55">
       <c r="A55" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C55" s="3" t="n">
         <v>4</v>
@@ -1980,15 +1977,15 @@
         <v>3</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C56" s="3" t="n">
         <v>1</v>
@@ -2005,10 +2002,10 @@
     </row>
     <row r="57">
       <c r="A57" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C57" s="3" t="n">
         <v>1</v>
@@ -2025,30 +2022,30 @@
     </row>
     <row r="58">
       <c r="A58" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C58" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E58" s="3" t="n">
         <v>3</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C59" s="3" t="n">
         <v>1</v>
@@ -2065,10 +2062,10 @@
     </row>
     <row r="60">
       <c r="A60" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C60" s="3" t="n">
         <v>1</v>
@@ -2085,10 +2082,10 @@
     </row>
     <row r="61">
       <c r="A61" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C61" s="3" t="n">
         <v>1</v>
@@ -2105,16 +2102,16 @@
     </row>
     <row r="62">
       <c r="A62" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="C62" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E62" s="3" t="n">
         <v>0</v>
@@ -2125,16 +2122,16 @@
     </row>
     <row r="63">
       <c r="A63" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C63" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E63" s="3" t="n">
         <v>0</v>
@@ -2145,36 +2142,36 @@
     </row>
     <row r="64">
       <c r="A64" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C64" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E64" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C65" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E65" s="3" t="n">
         <v>0</v>
@@ -2185,10 +2182,10 @@
     </row>
     <row r="66">
       <c r="A66" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B66" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="C66" s="3" t="n">
         <v>5</v>
@@ -2205,10 +2202,10 @@
     </row>
     <row r="67">
       <c r="A67" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C67" s="3" t="n">
         <v>4</v>
@@ -2225,10 +2222,10 @@
     </row>
     <row r="68">
       <c r="A68" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C68" s="3" t="n">
         <v>5</v>
@@ -2245,10 +2242,10 @@
     </row>
     <row r="69">
       <c r="A69" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C69" s="3" t="n">
         <v>1</v>
@@ -2265,16 +2262,16 @@
     </row>
     <row r="70">
       <c r="A70" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C70" s="3" t="n">
         <v>7</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E70" s="3" t="n">
         <v>2</v>
@@ -2285,10 +2282,10 @@
     </row>
     <row r="71">
       <c r="A71" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C71" s="3" t="n">
         <v>2</v>
@@ -2305,10 +2302,10 @@
     </row>
     <row r="72">
       <c r="A72" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C72" s="3" t="n">
         <v>1</v>
@@ -2325,10 +2322,10 @@
     </row>
     <row r="73">
       <c r="A73" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C73" s="3" t="n">
         <v>4</v>
@@ -2345,10 +2342,10 @@
     </row>
     <row r="74">
       <c r="A74" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C74" s="3" t="n">
         <v>5</v>
@@ -2365,11 +2362,11 @@
     </row>
     <row r="75">
       <c r="A75" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B75" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="C75" s="3" t="n">
         <v>1</v>
       </c>
@@ -2380,15 +2377,15 @@
         <v>1</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C76" s="3" t="n">
         <v>1</v>
@@ -2405,10 +2402,10 @@
     </row>
     <row r="77">
       <c r="A77" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C77" s="3" t="n">
         <v>1</v>
@@ -2425,10 +2422,10 @@
     </row>
     <row r="78">
       <c r="A78" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C78" s="3" t="n">
         <v>2</v>
@@ -2445,10 +2442,10 @@
     </row>
     <row r="79">
       <c r="A79" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C79" s="3" t="n">
         <v>4</v>
@@ -2465,10 +2462,10 @@
     </row>
     <row r="80">
       <c r="A80" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C80" s="3" t="n">
         <v>1</v>
@@ -2485,10 +2482,10 @@
     </row>
     <row r="81">
       <c r="A81" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C81" s="3" t="n">
         <v>4</v>
@@ -2500,15 +2497,15 @@
         <v>1</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C82" s="3" t="n">
         <v>2</v>
@@ -2520,15 +2517,15 @@
         <v>1</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C83" s="3" t="n">
         <v>5</v>
@@ -2545,10 +2542,10 @@
     </row>
     <row r="84">
       <c r="A84" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C84" s="3" t="n">
         <v>4</v>
@@ -2560,15 +2557,15 @@
         <v>1</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B85" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="C85" s="3" t="n">
         <v>1</v>
@@ -2585,10 +2582,10 @@
     </row>
     <row r="86">
       <c r="A86" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C86" s="3" t="n">
         <v>2</v>
@@ -2605,10 +2602,10 @@
     </row>
     <row r="87">
       <c r="A87" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C87" s="3" t="n">
         <v>1</v>
@@ -2625,10 +2622,10 @@
     </row>
     <row r="88">
       <c r="A88" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>1</v>
@@ -2645,10 +2642,10 @@
     </row>
     <row r="89">
       <c r="A89" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C89" s="3" t="n">
         <v>1</v>
@@ -2665,10 +2662,10 @@
     </row>
     <row r="90">
       <c r="A90" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C90" s="3" t="n">
         <v>1</v>
@@ -2685,30 +2682,30 @@
     </row>
     <row r="91">
       <c r="A91" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B91" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="C91" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E91" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B92" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>1</v>
@@ -2725,10 +2722,10 @@
     </row>
     <row r="93">
       <c r="A93" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C93" s="3" t="n">
         <v>4</v>
@@ -2745,16 +2742,16 @@
     </row>
     <row r="94">
       <c r="A94" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C94" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E94" s="3" t="n">
         <v>0</v>
@@ -2765,10 +2762,10 @@
     </row>
     <row r="95">
       <c r="A95" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C95" s="3" t="n">
         <v>2</v>
@@ -2785,10 +2782,10 @@
     </row>
     <row r="96">
       <c r="A96" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C96" s="3" t="n">
         <v>1</v>
@@ -2805,16 +2802,16 @@
     </row>
     <row r="97">
       <c r="A97" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C97" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E97" s="3" t="n">
         <v>2</v>
@@ -2825,10 +2822,10 @@
     </row>
     <row r="98">
       <c r="A98" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C98" s="3" t="n">
         <v>4</v>
@@ -2845,10 +2842,10 @@
     </row>
     <row r="99">
       <c r="A99" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>1</v>
@@ -2865,10 +2862,10 @@
     </row>
     <row r="100">
       <c r="A100" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C100" s="3" t="n">
         <v>1</v>
@@ -2885,10 +2882,10 @@
     </row>
     <row r="101">
       <c r="A101" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B101" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>1</v>
@@ -2905,10 +2902,10 @@
     </row>
     <row r="102">
       <c r="A102" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C102" s="3" t="n">
         <v>1</v>
@@ -2925,10 +2922,10 @@
     </row>
     <row r="103">
       <c r="A103" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C103" s="3" t="n">
         <v>2</v>
@@ -2945,10 +2942,10 @@
     </row>
     <row r="104">
       <c r="A104" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B104" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="C104" s="3" t="n">
         <v>1</v>
@@ -2965,10 +2962,10 @@
     </row>
     <row r="105">
       <c r="A105" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C105" s="3" t="n">
         <v>2</v>
@@ -2985,10 +2982,10 @@
     </row>
     <row r="106">
       <c r="A106" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>1</v>
@@ -3005,10 +3002,10 @@
     </row>
     <row r="107">
       <c r="A107" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C107" s="3" t="n">
         <v>1</v>
@@ -3025,16 +3022,16 @@
     </row>
     <row r="108">
       <c r="A108" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B108" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B108" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="C108" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E108" s="3" t="n">
         <v>0</v>
@@ -3045,10 +3042,10 @@
     </row>
     <row r="109">
       <c r="A109" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B109" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="B109" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="C109" s="3" t="n">
         <v>2</v>
@@ -3065,10 +3062,10 @@
     </row>
     <row r="110">
       <c r="A110" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C110" s="3" t="n">
         <v>6</v>
@@ -3085,10 +3082,10 @@
     </row>
     <row r="111">
       <c r="A111" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>1</v>
@@ -3105,10 +3102,10 @@
     </row>
     <row r="112">
       <c r="A112" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C112" s="3" t="n">
         <v>2</v>
@@ -3125,10 +3122,10 @@
     </row>
     <row r="113">
       <c r="A113" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C113" s="3" t="n">
         <v>1</v>
@@ -3145,10 +3142,10 @@
     </row>
     <row r="114">
       <c r="A114" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>1</v>
@@ -3165,10 +3162,10 @@
     </row>
     <row r="115">
       <c r="A115" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>1</v>
@@ -3185,10 +3182,10 @@
     </row>
     <row r="116">
       <c r="A116" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C116" s="3" t="n">
         <v>1</v>
@@ -3205,10 +3202,10 @@
     </row>
     <row r="117">
       <c r="A117" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C117" s="3" t="n">
         <v>1</v>
@@ -3225,10 +3222,10 @@
     </row>
     <row r="118">
       <c r="A118" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C118" s="3" t="n">
         <v>1</v>
@@ -3245,10 +3242,10 @@
     </row>
     <row r="119">
       <c r="A119" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C119" s="3" t="n">
         <v>1</v>
@@ -3265,10 +3262,10 @@
     </row>
     <row r="120">
       <c r="A120" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C120" s="3" t="n">
         <v>1</v>
@@ -3285,10 +3282,10 @@
     </row>
     <row r="121">
       <c r="A121" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B121" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="C121" s="3" t="n">
         <v>1</v>
@@ -3305,10 +3302,10 @@
     </row>
     <row r="122">
       <c r="A122" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C122" s="3" t="n">
         <v>1</v>
@@ -3325,10 +3322,10 @@
     </row>
     <row r="123">
       <c r="A123" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C123" s="3" t="n">
         <v>1</v>
@@ -3345,10 +3342,10 @@
     </row>
     <row r="124">
       <c r="A124" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C124" s="3" t="n">
         <v>1</v>
@@ -3365,10 +3362,10 @@
     </row>
     <row r="125">
       <c r="A125" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>1</v>
@@ -3385,10 +3382,10 @@
     </row>
     <row r="126">
       <c r="A126" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C126" s="3" t="n">
         <v>1</v>
@@ -3405,10 +3402,10 @@
     </row>
     <row r="127">
       <c r="A127" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C127" s="3" t="n">
         <v>1</v>
@@ -3425,16 +3422,16 @@
     </row>
     <row r="128">
       <c r="A128" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C128" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E128" s="3" t="n">
         <v>0</v>
@@ -3445,16 +3442,16 @@
     </row>
     <row r="129">
       <c r="A129" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C129" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E129" s="3" t="n">
         <v>0</v>
@@ -3465,10 +3462,10 @@
     </row>
     <row r="130">
       <c r="A130" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="B130" s="9" t="s">
         <v>156</v>
-      </c>
-      <c r="B130" s="9" t="s">
-        <v>157</v>
       </c>
       <c r="C130" s="10" t="n">
         <v>5</v>
